--- a/output/pdf_financials_xlsx/QBR.B.xlsx
+++ b/output/pdf_financials_xlsx/QBR.B.xlsx
@@ -1388,19 +1388,19 @@
         <v>-112.8</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-171.9</v>
+        <v>-117.8</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-265.9</v>
+        <v>-127.6999999999999</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-197.1</v>
+        <v>-159</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>-113.7</v>
+        <v>-108.2</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-182.8</v>
+        <v>-172.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>-197</v>
@@ -1628,7 +1628,7 @@
         <v>230.1</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>201</v>
+        <v>383</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>259</v>
@@ -1808,10 +1808,10 @@
         <v>277.7</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>225.3</v>
+        <v>456.6</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>201</v>
+        <v>383</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>255.3</v>
@@ -1826,19 +1826,19 @@
         <v>180.1</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>194.7</v>
+        <v>248.8</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>390.5</v>
+        <v>528.7</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>403.7</v>
+        <v>441.8</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>652.8</v>
+        <v>658.3</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>607.2</v>
+        <v>617.4</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>588.4</v>
@@ -2422,19 +2422,19 @@
         <v>38.51143735063162</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>46.89034369885434</v>
+        <v>32.13311511183852</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>40.50883607556368</v>
+        <v>19.45460085313832</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>32.80625832223702</v>
+        <v>26.46471371504661</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>14.83365949119374</v>
+        <v>14.11611219830398</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>23.13924050632911</v>
+        <v>21.84810126582278</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>25.08276037687802</v>
@@ -2465,10 +2465,10 @@
         <v>7.295607398066414</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>5.632359191020225</v>
+        <v>11.4147146321342</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>4.778205676793609</v>
+        <v>9.104740170208718</v>
       </c>
       <c r="F32" s="3" t="n">
         <v>6.008613994210267</v>
@@ -2483,19 +2483,19 @@
         <v>4.628868099105583</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>4.847383359059902</v>
+        <v>6.194293681222924</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>9.46643717728055</v>
+        <v>12.81665899008509</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>9.655584788328152</v>
+        <v>10.56685003587658</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>15.20331640970702</v>
+        <v>15.33140807676184</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>14.06271712446153</v>
+        <v>14.29894853860763</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>12.91937467064816</v>
@@ -6551,62 +6551,52 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>73.8</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>120.9</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>138.6</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>630.7</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>661.1</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>693.6</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>653</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>707.9</v>
+      </c>
+      <c r="L100" s="3" t="n">
+        <v>716.7</v>
+      </c>
+      <c r="M100" s="3" t="n">
+        <v>714.9</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>803.2</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>783.8</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>767.7</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>943.3</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>858</v>
       </c>
     </row>
     <row r="101">
@@ -8325,19 +8315,19 @@
         <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-42</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-46.5</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-40.6</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>0</v>
+        <v>-24.8</v>
       </c>
       <c r="I126" s="1" t="inlineStr">
         <is>
@@ -8365,16 +8355,16 @@
         </is>
       </c>
       <c r="N126" s="3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="Q126" s="3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="R126" s="3" t="n">
         <v>0</v>
@@ -50490,7 +50480,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -50596,7 +50590,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -50702,7 +50696,11 @@
           <t>Depreciation of right-of-use assets 12</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -53736,7 +53734,11 @@
           <t>Depreciation of property, plant and equipment 11</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E437" t="inlineStr">
         <is>
           <t>-</t>
@@ -53840,7 +53842,7 @@
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
@@ -53944,7 +53946,11 @@
           <t>Depreciation of right-of-use assets 13</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -56152,7 +56158,11 @@
           <t>Additions to intangible assets 12</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
@@ -56256,7 +56266,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E462" t="inlineStr">
         <is>
           <t>-</t>
@@ -58020,7 +58034,11 @@
           <t>Depreciation of property, plant and equipment 13</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E481" t="inlineStr">
         <is>
           <t>-</t>
@@ -58124,7 +58142,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -58224,7 +58242,11 @@
           <t>Depreciation of right-of-use assets 15</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E483" t="inlineStr">
         <is>
           <t>-</t>
@@ -58946,7 +58968,11 @@
           <t>Additions to intangible assets 14</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E490" t="inlineStr">
         <is>
           <t>-</t>
@@ -61506,7 +61532,11 @@
           <t>Depreciation of property, plant and equipment 12</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E516" t="inlineStr">
         <is>
           <t>-</t>
@@ -61612,7 +61642,7 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -62136,7 +62166,11 @@
           <t>Additions to intangible assets 13</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E522" t="inlineStr">
         <is>
           <t>-</t>
@@ -64050,7 +64084,11 @@
           <t>Depreciation of property, plant and equipment 15</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr"/>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E541" t="inlineStr">
         <is>
           <t>-</t>
@@ -64148,7 +64186,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -65486,7 +65524,11 @@
           <t>Additions to intangible assets 16</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr"/>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E555" t="inlineStr">
         <is>
           <t>-</t>
@@ -67496,7 +67538,11 @@
           <t>Depreciation of property, plant and equipment 14</t>
         </is>
       </c>
-      <c r="D575" t="inlineStr"/>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E575" t="inlineStr">
         <is>
           <t>-</t>
@@ -67602,7 +67648,7 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -68320,7 +68366,11 @@
           <t>Additions to intangible assets 15</t>
         </is>
       </c>
-      <c r="D583" t="inlineStr"/>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E583" t="inlineStr">
         <is>
           <t>-</t>
@@ -75482,7 +75532,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D652" t="inlineStr"/>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E652" s="5" t="n">
         <v>-637.6</v>
       </c>
@@ -83274,11 +83328,7 @@
           <t>Shareholders $</t>
         </is>
       </c>
-      <c r="D729" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D729" t="inlineStr"/>
       <c r="E729" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QBR.B.xlsx
+++ b/output/pdf_financials_xlsx/QBR.B.xlsx
@@ -1618,8 +1618,10 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>188</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C20" s="3" t="n">
         <v>276.1</v>
@@ -1680,10 +1682,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>383.3</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1695,28 +1697,28 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-193.8</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-81.59999999999999</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0</v>
+        <v>-19.7</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0</v>
+        <v>18.2</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>33.2</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>0</v>
@@ -6484,7 +6486,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>188</v>
+        <v>-195.3</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>276.1</v>
@@ -6499,7 +6501,7 @@
         <v>259</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-185.3</v>
+        <v>-126.9</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>57.2</v>
@@ -8603,13 +8605,13 @@
         </is>
       </c>
       <c r="O129" s="3" t="n">
-        <v>119.5</v>
+        <v>281.9</v>
       </c>
       <c r="P129" s="3" t="n">
-        <v>0</v>
+        <v>-812.6</v>
       </c>
       <c r="Q129" s="3" t="n">
-        <v>0</v>
+        <v>1180.5</v>
       </c>
       <c r="R129" s="3" t="n">
         <v>-712.2</v>
@@ -8676,25 +8678,17 @@
       <c r="O130" s="3" t="n">
         <v>136.7</v>
       </c>
-      <c r="P130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P130" s="3" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="Q130" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="R130" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="S130" s="3" t="n">
+        <v>96</v>
       </c>
     </row>
     <row r="131">
@@ -8824,13 +8818,13 @@
         <v>122.7</v>
       </c>
       <c r="O132" s="3" t="n">
-        <v>-72</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="P132" s="3" t="n">
-        <v>631.4</v>
+        <v>-181.2</v>
       </c>
       <c r="Q132" s="3" t="n">
-        <v>-1215.3</v>
+        <v>-34.8</v>
       </c>
       <c r="R132" s="3" t="n">
         <v>84.90000000000001</v>
@@ -8895,27 +8889,19 @@
         <v>136.7</v>
       </c>
       <c r="O133" s="3" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="P133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>227.1</v>
+      </c>
+      <c r="P133" s="3" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="Q133" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="R133" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="S133" s="3" t="n">
+        <v>195.8</v>
       </c>
     </row>
     <row r="134">
@@ -53532,7 +53518,11 @@
           <t>Cash, cash equivalents and restricted cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E435" t="inlineStr">
         <is>
           <t>-</t>
@@ -53630,7 +53620,11 @@
           <t>Cash, cash equivalents and restricted cash at end of the year 28 $</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -55464,7 +55458,11 @@
           <t>Cash, cash equivalents and restricted cash at end of the year 30 $</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E454" t="inlineStr">
         <is>
           <t>-</t>
@@ -56566,7 +56564,11 @@
           <t>Cash, cash equivalents and restricted cash at end of the year $</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E465" t="inlineStr">
         <is>
           <t>-</t>
@@ -69296,7 +69298,11 @@
           <t>Income (loss) from continuing operations $</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E592" s="5" t="n">
         <v>-195.3</v>
       </c>
@@ -75014,7 +75020,11 @@
           <t>Future income taxes 8</t>
         </is>
       </c>
-      <c r="D647" t="inlineStr"/>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E647" t="inlineStr">
         <is>
           <t>-</t>
@@ -77732,7 +77742,11 @@
           <t>Future income taxes (note 7)</t>
         </is>
       </c>
-      <c r="D673" t="inlineStr"/>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E673" s="5" t="n">
         <v>127.7</v>
       </c>
@@ -83034,7 +83048,11 @@
           <t>Income from discontinued operations 32</t>
         </is>
       </c>
-      <c r="D726" t="inlineStr"/>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E726" t="inlineStr">
         <is>
           <t>-</t>
@@ -85110,7 +85128,11 @@
           <t>Income from discontinued operations 31</t>
         </is>
       </c>
-      <c r="D748" t="inlineStr"/>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E748" t="inlineStr">
         <is>
           <t>-</t>
@@ -85946,7 +85968,11 @@
           <t>Income from discontinued operations 32</t>
         </is>
       </c>
-      <c r="D756" t="inlineStr"/>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E756" t="inlineStr">
         <is>
           <t>-</t>
@@ -87068,7 +87094,11 @@
           <t>Income from discontinued operations</t>
         </is>
       </c>
-      <c r="D767" t="inlineStr"/>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E767" t="inlineStr">
         <is>
           <t>-</t>
@@ -87676,7 +87706,11 @@
           <t>Loss from discontinued operations 31</t>
         </is>
       </c>
-      <c r="D773" t="inlineStr"/>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E773" t="inlineStr">
         <is>
           <t>-</t>
@@ -87882,7 +87916,11 @@
           <t>Loss from discontinued operations 10</t>
         </is>
       </c>
-      <c r="D775" t="inlineStr"/>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E775" t="inlineStr">
         <is>
           <t>-</t>
@@ -88934,7 +88972,11 @@
           <t>Loss from discontinued operations 8</t>
         </is>
       </c>
-      <c r="D785" t="inlineStr"/>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E785" t="inlineStr">
         <is>
           <t>-</t>
@@ -94038,7 +94080,11 @@
           <t>Income from discontinued operations</t>
         </is>
       </c>
-      <c r="D834" t="inlineStr"/>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E834" t="inlineStr">
         <is>
           <t>-</t>
@@ -95518,7 +95564,11 @@
           <t>Income from discontinued operations (note 26)</t>
         </is>
       </c>
-      <c r="D848" t="inlineStr"/>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E848" s="5" t="n">
         <v>383.3</v>
       </c>
